--- a/public/templates/examples/A-083-RiskFindingRegister-EXAMPLE-S.xlsx
+++ b/public/templates/examples/A-083-RiskFindingRegister-EXAMPLE-S.xlsx
@@ -19,7 +19,7 @@
   <numFmts count="0"/>
   <fonts count="8">
     <font>
-      <name val="Calibri"/>
+      <name val="Aptos"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
@@ -224,12 +224,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>0</col>
+      <col>9</col>
       <colOff>0</colOff>
       <row>0</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="552450" cy="552450"/>
+    <ext cx="857250" cy="857250"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -343,7 +343,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -377,7 +377,7 @@
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>

--- a/public/templates/examples/A-083-RiskFindingRegister-EXAMPLE-S.xlsx
+++ b/public/templates/examples/A-083-RiskFindingRegister-EXAMPLE-S.xlsx
@@ -4,19 +4,21 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Form" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+  </numFmts>
   <fonts count="8">
     <font>
       <name val="Aptos"/>
@@ -111,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -144,6 +146,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="164" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -587,7 +593,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:J35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -739,7 +745,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1">
+    <row r="13" ht="34.7" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Finding ID</t>
@@ -791,7 +797,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="50.5" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
           <t>F-01</t>
@@ -827,10 +833,8 @@
           <t>Enable a monthly patch window with the county IT contact</t>
         </is>
       </c>
-      <c r="H14" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
+      <c r="H14" s="14">
+        <v>46203</v>
       </c>
       <c r="I14" s="9" t="inlineStr">
         <is>
@@ -839,7 +843,7 @@
       </c>
       <c r="J14" s="9" t="inlineStr"/>
     </row>
-    <row r="15">
+    <row r="15" ht="50.5" customHeight="1">
       <c r="A15" s="9" t="inlineStr">
         <is>
           <t>F-02</t>
@@ -875,10 +879,8 @@
           <t>Turn on MFA through the CAD vendor</t>
         </is>
       </c>
-      <c r="H15" s="9" t="inlineStr">
-        <is>
-          <t>2026-07-15</t>
-        </is>
+      <c r="H15" s="14">
+        <v>46218</v>
       </c>
       <c r="I15" s="9" t="inlineStr">
         <is>
@@ -887,7 +889,7 @@
       </c>
       <c r="J15" s="9" t="inlineStr"/>
     </row>
-    <row r="16">
+    <row r="16" ht="50.5" customHeight="1">
       <c r="A16" s="9" t="inlineStr">
         <is>
           <t>F-03</t>
@@ -923,10 +925,8 @@
           <t>Price a cellular failover circuit for the budget cycle</t>
         </is>
       </c>
-      <c r="H16" s="9" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
+      <c r="H16" s="14">
+        <v>46295</v>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
@@ -935,7 +935,7 @@
       </c>
       <c r="J16" s="9" t="inlineStr"/>
     </row>
-    <row r="17">
+    <row r="17" ht="50.5" customHeight="1">
       <c r="A17" s="9" t="inlineStr">
         <is>
           <t>F-04</t>
@@ -971,10 +971,8 @@
           <t>Install a keyed lock; relocate supplies</t>
         </is>
       </c>
-      <c r="H17" s="9" t="inlineStr">
-        <is>
-          <t>2026-05-31</t>
-        </is>
+      <c r="H17" s="14">
+        <v>46173</v>
       </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
@@ -990,7 +988,7 @@
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
         <is>
-          <t>Status Summary</t>
+          <t>Status Summary (as of 2026-07-01)</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1000,6 @@
       </c>
       <c r="C20" s="11">
         <f>COUNTA(A14:A17)</f>
-        <v/>
       </c>
     </row>
     <row r="21">
@@ -1013,7 +1010,6 @@
       </c>
       <c r="C21" s="11">
         <f>COUNTIF(I14:I17,"Open")</f>
-        <v/>
       </c>
     </row>
     <row r="22">
@@ -1024,7 +1020,6 @@
       </c>
       <c r="C22" s="11">
         <f>COUNTIF(I14:I17,"In Progress")</f>
-        <v/>
       </c>
     </row>
     <row r="23">
@@ -1034,8 +1029,7 @@
         </is>
       </c>
       <c r="C23" s="11">
-        <f>COUNTIFS(H14:H17,"&lt;"&amp;TODAY(),I14:I17,"Open")+COUNTIFS(H14:H17,"&lt;"&amp;TODAY(),I14:I17,"In Progress")</f>
-        <v/>
+        <f>COUNTIFS(H14:H17,"&lt;"&amp;DATE(2026,7,1),I14:I17,"Open")+COUNTIFS(H14:H17,"&lt;"&amp;DATE(2026,7,1),I14:I17,"In Progress")</f>
       </c>
     </row>
     <row r="24">
@@ -1046,7 +1040,6 @@
       </c>
       <c r="C24" s="11">
         <f>COUNTIF(I14:I17,"Risk Accepted")</f>
-        <v/>
       </c>
     </row>
     <row r="25">
@@ -1057,7 +1050,6 @@
       </c>
       <c r="C25" s="11">
         <f>COUNTIF(I14:I17,"Closed")</f>
-        <v/>
       </c>
     </row>
     <row r="26">
@@ -1126,10 +1118,8 @@
           <t>Tracy Holloway</t>
         </is>
       </c>
-      <c r="D31" s="13" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
+      <c r="D31" s="15">
+        <v>46174</v>
       </c>
     </row>
     <row r="33">
@@ -1161,16 +1151,14 @@
         </is>
       </c>
     </row>
-    <row r="35">
+    <row r="35" ht="34.7" customHeight="1">
       <c r="A35" s="9" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B35" s="9" t="inlineStr">
-        <is>
-          <t>2026-06-01</t>
-        </is>
+      <c r="B35" s="14">
+        <v>46174</v>
       </c>
       <c r="C35" s="9" t="inlineStr">
         <is>
@@ -1213,7 +1201,8 @@
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A33:J33"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>